--- a/app/assets/Datos/Faltantes_Corregida.xlsx
+++ b/app/assets/Datos/Faltantes_Corregida.xlsx
@@ -5,25 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eagel\OneDrive\Escritorio\Lalo\Escuela\Gob\Proyectos\CEEA_Mapa_nivel_pozo\app\assets\Datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIGEH\Desktop\Lalo\Gob\Proyectos\CEEA_Mapa_nivel_pozo\app\assets\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015239A1-C9BD-4035-ADAA-52CB3FA04BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C79C88-2678-4AA1-9B16-5374C32A1A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$E$1:$E$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AD$157</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="834">
   <si>
     <t>Año</t>
   </si>
@@ -448,9 +448,6 @@
     <t>Plan Grande</t>
   </si>
   <si>
-    <t>Plan Grande (El Puente)</t>
-  </si>
-  <si>
     <t>Túnel Neptón</t>
   </si>
   <si>
@@ -1699,9 +1696,6 @@
     <t>Orizatlan</t>
   </si>
   <si>
-    <t>Orizatlán</t>
-  </si>
-  <si>
     <t>224.24</t>
   </si>
   <si>
@@ -2149,9 +2143,6 @@
     <t>Zacualtipan</t>
   </si>
   <si>
-    <t>Cacala</t>
-  </si>
-  <si>
     <t>Manantial Cacala</t>
   </si>
   <si>
@@ -2296,9 +2287,6 @@
     <t>San Agustin Tlaxiaca (Barrio Casa Grande)</t>
   </si>
   <si>
-    <t>Barrio Casa Grande</t>
-  </si>
-  <si>
     <t>Toma Domiciliaria (calle Nicolas Bravo)</t>
   </si>
   <si>
@@ -2323,9 +2311,6 @@
     <t>San Agustin Tlaxiaca (Mexiquito)</t>
   </si>
   <si>
-    <t>Barrio Mexiquito</t>
-  </si>
-  <si>
     <t>Toma Domociliaria (Red de Distribucion)</t>
   </si>
   <si>
@@ -2507,9 +2492,6 @@
   </si>
   <si>
     <t>Col. 20 De Noviembre</t>
-  </si>
-  <si>
-    <t>Morelos</t>
   </si>
   <si>
     <t>Pozo 20 de Noviembre</t>
@@ -2529,6 +2511,21 @@
   </si>
   <si>
     <t>San Nicolás el Chico [Rancho]</t>
+  </si>
+  <si>
+    <t>Plan Grande (Ejido el Puente)</t>
+  </si>
+  <si>
+    <t>Casa Grande [Barrio]</t>
+  </si>
+  <si>
+    <t>San José Bojay el Grande</t>
+  </si>
+  <si>
+    <t>San Felipe Orizatlan</t>
+  </si>
+  <si>
+    <t>Zacualtipán</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2536,7 @@
     <numFmt numFmtId="164" formatCode="d\.m"/>
     <numFmt numFmtId="165" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2556,6 +2553,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2578,7 +2581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2598,6 +2601,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2817,16 +2821,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AD157"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.90625" customWidth="1"/>
-    <col min="4" max="4" width="32.08984375" customWidth="1"/>
-    <col min="5" max="5" width="21.7265625" customWidth="1"/>
-    <col min="6" max="6" width="25.6328125" customWidth="1"/>
-    <col min="7" max="7" width="30.90625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="32.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.77734375" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2918,7 +2922,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2012</v>
       </c>
@@ -3010,7 +3014,7 @@
         <v>45835</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2012</v>
       </c>
@@ -3102,7 +3106,7 @@
         <v>45714</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2012</v>
       </c>
@@ -3194,7 +3198,7 @@
         <v>45918</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2012</v>
       </c>
@@ -3286,7 +3290,7 @@
         <v>45773</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2012</v>
       </c>
@@ -3378,7 +3382,7 @@
         <v>45739</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2012</v>
       </c>
@@ -3470,7 +3474,7 @@
         <v>45895</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2012</v>
       </c>
@@ -3562,7 +3566,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2012</v>
       </c>
@@ -3654,7 +3658,7 @@
         <v>45731</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2012</v>
       </c>
@@ -3746,7 +3750,7 @@
         <v>45794</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2013</v>
       </c>
@@ -3838,7 +3842,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2013</v>
       </c>
@@ -3855,7 +3859,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>115</v>
@@ -3930,7 +3934,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>2013</v>
       </c>
@@ -4022,7 +4026,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -4114,7 +4118,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>2014</v>
       </c>
@@ -4206,7 +4210,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>2014</v>
       </c>
@@ -4223,10 +4227,10 @@
         <v>94</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>35</v>
@@ -4247,7 +4251,7 @@
         <v>63</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>39</v>
@@ -4256,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R16" s="3">
         <v>2</v>
@@ -4268,19 +4272,19 @@
         <v>45779</v>
       </c>
       <c r="U16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="V16" s="2" t="s">
+      <c r="W16" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="X16" s="3">
         <v>1</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z16" s="2">
         <v>580</v>
@@ -4298,7 +4302,7 @@
         <v>45831</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>2014</v>
       </c>
@@ -4306,19 +4310,19 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>62</v>
@@ -4357,13 +4361,13 @@
         <v>45690</v>
       </c>
       <c r="T17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="U17" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="V17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="W17" s="4">
         <v>45749</v>
@@ -4375,7 +4379,7 @@
         <v>85</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA17" s="2">
         <v>120</v>
@@ -4390,7 +4394,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>2014</v>
       </c>
@@ -4398,19 +4402,19 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>35</v>
@@ -4452,7 +4456,7 @@
         <v>101</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>77</v>
@@ -4473,7 +4477,7 @@
         <v>18</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AC18" s="2">
         <v>550</v>
@@ -4482,7 +4486,7 @@
         <v>45745</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>2014</v>
       </c>
@@ -4490,19 +4494,19 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>35</v>
@@ -4541,10 +4545,10 @@
         <v>0</v>
       </c>
       <c r="T19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>77</v>
@@ -4556,7 +4560,7 @@
         <v>3</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z19" s="2">
         <v>236</v>
@@ -4574,7 +4578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>2014</v>
       </c>
@@ -4582,19 +4586,19 @@
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>35</v>
@@ -4606,7 +4610,7 @@
         <v>28</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>36</v>
@@ -4633,10 +4637,10 @@
         <v>37</v>
       </c>
       <c r="T20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="U20" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="V20" s="2" t="s">
         <v>104</v>
@@ -4648,13 +4652,13 @@
         <v>6</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Z20" s="4">
         <v>45699</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>63</v>
@@ -4666,7 +4670,7 @@
         <v>45795</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>2015</v>
       </c>
@@ -4674,19 +4678,19 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>35</v>
@@ -4704,7 +4708,7 @@
         <v>36</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>65</v>
@@ -4728,7 +4732,7 @@
         <v>45839</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V21" s="2">
         <v>0</v>
@@ -4743,7 +4747,7 @@
         <v>45815</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA21" s="2">
         <v>10</v>
@@ -4752,13 +4756,13 @@
         <v>63</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AD21" s="4">
         <v>45920</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>2015</v>
       </c>
@@ -4766,19 +4770,19 @@
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>35</v>
@@ -4820,10 +4824,10 @@
         <v>45713</v>
       </c>
       <c r="U22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="V22" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="W22" s="4">
         <v>45778</v>
@@ -4832,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Z22" s="2">
         <v>662</v>
@@ -4850,7 +4854,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>2016</v>
       </c>
@@ -4861,16 +4865,16 @@
         <v>45</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>35</v>
@@ -4888,10 +4892,10 @@
         <v>36</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O23" s="2">
         <v>0</v>
@@ -4909,10 +4913,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="U23" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="V23" s="2">
         <v>0</v>
@@ -4927,7 +4931,7 @@
         <v>45907</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AA23" s="2">
         <v>0</v>
@@ -4942,7 +4946,7 @@
         <v>45736</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>2016</v>
       </c>
@@ -4953,16 +4957,16 @@
         <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="F24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>35</v>
@@ -4980,7 +4984,7 @@
         <v>36</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>43</v>
@@ -5004,7 +5008,7 @@
         <v>45849</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V24" s="2">
         <v>0</v>
@@ -5016,10 +5020,10 @@
         <v>3</v>
       </c>
       <c r="Y24" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z24" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="AA24" s="4">
         <v>45910</v>
@@ -5034,7 +5038,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>2016</v>
       </c>
@@ -5042,7 +5046,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>132</v>
@@ -5054,7 +5058,7 @@
         <v>132</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>35</v>
@@ -5093,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="T25" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="U25" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>40</v>
@@ -5108,7 +5112,7 @@
         <v>3</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z25" s="2">
         <v>471</v>
@@ -5126,7 +5130,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>2016</v>
       </c>
@@ -5134,19 +5138,19 @@
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>35</v>
@@ -5185,10 +5189,10 @@
         <v>0</v>
       </c>
       <c r="T26" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="U26" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>104</v>
@@ -5200,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z26" s="2">
         <v>563</v>
@@ -5218,7 +5222,7 @@
         <v>45710</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>2016</v>
       </c>
@@ -5229,16 +5233,16 @@
         <v>132</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>35</v>
@@ -5277,13 +5281,13 @@
         <v>37</v>
       </c>
       <c r="T27" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="U27" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="V27" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="W27" s="4">
         <v>45813</v>
@@ -5310,7 +5314,7 @@
         <v>45895</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>2016</v>
       </c>
@@ -5321,16 +5325,16 @@
         <v>132</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>35</v>
@@ -5360,22 +5364,22 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R28" s="3">
         <v>1</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T28" s="4">
         <v>45838</v>
       </c>
       <c r="U28" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="V28" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>77</v>
@@ -5384,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Z28" s="2">
         <v>300</v>
@@ -5402,7 +5406,7 @@
         <v>45859</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>2016</v>
       </c>
@@ -5410,19 +5414,19 @@
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>35</v>
@@ -5440,7 +5444,7 @@
         <v>36</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N29" s="2">
         <v>0</v>
@@ -5464,7 +5468,7 @@
         <v>45784</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V29" s="2">
         <v>0</v>
@@ -5479,7 +5483,7 @@
         <v>45754</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA29" s="2">
         <v>8</v>
@@ -5494,7 +5498,7 @@
         <v>45858</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>2016</v>
       </c>
@@ -5502,19 +5506,19 @@
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>35</v>
@@ -5532,7 +5536,7 @@
         <v>36</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>65</v>
@@ -5556,7 +5560,7 @@
         <v>45914</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V30" s="3">
         <v>8</v>
@@ -5571,7 +5575,7 @@
         <v>45845</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AA30" s="2">
         <v>6</v>
@@ -5586,7 +5590,7 @@
         <v>45858</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>2016</v>
       </c>
@@ -5594,19 +5598,19 @@
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>35</v>
@@ -5624,7 +5628,7 @@
         <v>36</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N31" s="2">
         <v>0</v>
@@ -5648,10 +5652,10 @@
         <v>45726</v>
       </c>
       <c r="U31" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="V31" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="W31" s="4">
         <v>45719</v>
@@ -5678,7 +5682,7 @@
         <v>45679</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>2016</v>
       </c>
@@ -5686,19 +5690,19 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>35</v>
@@ -5740,7 +5744,7 @@
         <v>45881</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V32" s="2">
         <v>0</v>
@@ -5752,10 +5756,10 @@
         <v>8</v>
       </c>
       <c r="Y32" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z32" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="AA32" s="2">
         <v>10</v>
@@ -5770,7 +5774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>2016</v>
       </c>
@@ -5778,7 +5782,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>30</v>
@@ -5790,7 +5794,7 @@
         <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>35</v>
@@ -5829,28 +5833,28 @@
         <v>65</v>
       </c>
       <c r="T33" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="U33" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X33" s="3">
         <v>37</v>
       </c>
       <c r="Y33" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z33" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="Z33" s="2" t="s">
+      <c r="AA33" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="AA33" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>63</v>
@@ -5859,10 +5863,10 @@
         <v>258</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>2016</v>
       </c>
@@ -5870,19 +5874,19 @@
         <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>35</v>
@@ -5921,25 +5925,25 @@
         <v>0</v>
       </c>
       <c r="T34" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="U34" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="V34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X34" s="3">
         <v>2</v>
       </c>
       <c r="Y34" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z34" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="Z34" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="AA34" s="2">
         <v>6</v>
@@ -5951,10 +5955,10 @@
         <v>263</v>
       </c>
       <c r="AD34" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>2016</v>
       </c>
@@ -5965,16 +5969,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>35</v>
@@ -6016,7 +6020,7 @@
         <v>45811</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>134</v>
@@ -6040,13 +6044,13 @@
         <v>0</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AD35" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>2016</v>
       </c>
@@ -6066,7 +6070,7 @@
         <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>35</v>
@@ -6108,7 +6112,7 @@
         <v>33</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>107</v>
@@ -6120,10 +6124,10 @@
         <v>0</v>
       </c>
       <c r="Y36" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z36" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="Z36" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="AA36" s="2">
         <v>0</v>
@@ -6138,7 +6142,7 @@
         <v>45714</v>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>2016</v>
       </c>
@@ -6149,16 +6153,16 @@
         <v>30</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>35</v>
@@ -6176,7 +6180,7 @@
         <v>36</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N37" s="2">
         <v>0</v>
@@ -6200,10 +6204,10 @@
         <v>45693</v>
       </c>
       <c r="U37" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="V37" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>75</v>
@@ -6212,7 +6216,7 @@
         <v>1</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z37" s="2">
         <v>288</v>
@@ -6230,7 +6234,7 @@
         <v>45774</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>2016</v>
       </c>
@@ -6241,16 +6245,16 @@
         <v>50</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>35</v>
@@ -6292,10 +6296,10 @@
         <v>45781</v>
       </c>
       <c r="U38" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="V38" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>49</v>
@@ -6304,7 +6308,7 @@
         <v>4</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>73</v>
@@ -6316,13 +6320,13 @@
         <v>65</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AD38" s="4">
         <v>45740</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>2016</v>
       </c>
@@ -6333,16 +6337,16 @@
         <v>50</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>35</v>
@@ -6384,7 +6388,7 @@
         <v>45864</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>75</v>
@@ -6396,10 +6400,10 @@
         <v>1</v>
       </c>
       <c r="Y39" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z39" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="Z39" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="AA39" s="2">
         <v>40</v>
@@ -6414,7 +6418,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>2016</v>
       </c>
@@ -6425,13 +6429,13 @@
         <v>57</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>111</v>
@@ -6476,10 +6480,10 @@
         <v>45828</v>
       </c>
       <c r="U40" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="V40" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="W40" s="4">
         <v>45658</v>
@@ -6494,7 +6498,7 @@
         <v>137</v>
       </c>
       <c r="AA40" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>39</v>
@@ -6506,7 +6510,7 @@
         <v>45837</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2016</v>
       </c>
@@ -6517,16 +6521,16 @@
         <v>57</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>35</v>
@@ -6544,7 +6548,7 @@
         <v>36</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N41" s="2">
         <v>0</v>
@@ -6556,22 +6560,22 @@
         <v>0</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R41" s="2">
         <v>0</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T41" s="4">
         <v>45817</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W41" s="4">
         <v>45691</v>
@@ -6580,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z41" s="2">
         <v>216</v>
@@ -6598,7 +6602,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="42" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>2016</v>
       </c>
@@ -6606,19 +6610,19 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
@@ -6636,7 +6640,7 @@
         <v>36</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N42" s="2">
         <v>0</v>
@@ -6660,10 +6664,10 @@
         <v>45871</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W42" s="4">
         <v>45809</v>
@@ -6681,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AC42" s="2">
         <v>494</v>
@@ -6690,7 +6694,7 @@
         <v>45899</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>2016</v>
       </c>
@@ -6698,19 +6702,19 @@
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>35</v>
@@ -6749,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="U43" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="V43" s="5">
         <v>45810</v>
@@ -6764,7 +6768,7 @@
         <v>576</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z43" s="2">
         <v>740</v>
@@ -6782,7 +6786,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>2016</v>
       </c>
@@ -6790,19 +6794,19 @@
         <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>35</v>
@@ -6844,7 +6848,7 @@
         <v>45752</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>82</v>
@@ -6856,7 +6860,7 @@
         <v>5</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Z44" s="2">
         <v>206</v>
@@ -6874,7 +6878,7 @@
         <v>45833</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>2016</v>
       </c>
@@ -6882,19 +6886,19 @@
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>35</v>
@@ -6915,7 +6919,7 @@
         <v>37</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>39</v>
@@ -6930,13 +6934,13 @@
         <v>8</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T45" s="4">
         <v>45906</v>
       </c>
       <c r="U45" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>123</v>
@@ -6948,25 +6952,25 @@
         <v>13</v>
       </c>
       <c r="Y45" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z45" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="Z45" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="AA45" s="2">
         <v>24</v>
       </c>
       <c r="AB45" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC45" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="AC45" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="AD45" s="4">
         <v>45736</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>2016</v>
       </c>
@@ -6974,19 +6978,19 @@
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>35</v>
@@ -7004,7 +7008,7 @@
         <v>36</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N46" s="2">
         <v>0</v>
@@ -7028,7 +7032,7 @@
         <v>45814</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>75</v>
@@ -7040,25 +7044,25 @@
         <v>2</v>
       </c>
       <c r="Y46" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="Z46" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="Z46" s="2" t="s">
+      <c r="AA46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="AA46" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="AD46" s="4">
         <v>45773</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>2016</v>
       </c>
@@ -7066,19 +7070,19 @@
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>35</v>
@@ -7099,7 +7103,7 @@
         <v>82</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>75</v>
@@ -7108,19 +7112,19 @@
         <v>0</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="R47" s="3">
         <v>7</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T47" s="4">
         <v>45722</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>43</v>
@@ -7132,7 +7136,7 @@
         <v>17</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Z47" s="2">
         <v>132</v>
@@ -7144,13 +7148,13 @@
         <v>40</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AD47" s="4">
         <v>45710</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>2016</v>
       </c>
@@ -7158,19 +7162,19 @@
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>35</v>
@@ -7206,16 +7210,16 @@
         <v>1</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T48" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="U48" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="V48" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="V48" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="W48" s="4">
         <v>45718</v>
@@ -7224,7 +7228,7 @@
         <v>5</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Z48" s="2">
         <v>389</v>
@@ -7233,7 +7237,7 @@
         <v>117</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AC48" s="2">
         <v>2003</v>
@@ -7242,7 +7246,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>2016</v>
       </c>
@@ -7250,19 +7254,19 @@
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>35</v>
@@ -7304,13 +7308,13 @@
         <v>45779</v>
       </c>
       <c r="U49" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="V49" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="V49" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="W49" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X49" s="3">
         <v>4</v>
@@ -7328,13 +7332,13 @@
         <v>37</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AD49" s="4">
         <v>45915</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>2016</v>
       </c>
@@ -7342,19 +7346,19 @@
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>35</v>
@@ -7372,7 +7376,7 @@
         <v>36</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N50" s="2">
         <v>0</v>
@@ -7384,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R50" s="2">
         <v>0</v>
@@ -7396,22 +7400,22 @@
         <v>45719</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
       </c>
       <c r="Y50" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="Z50" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="Z50" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="AA50" s="2">
         <v>1</v>
@@ -7426,7 +7430,7 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>2016</v>
       </c>
@@ -7437,16 +7441,16 @@
         <v>78</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>35</v>
@@ -7464,7 +7468,7 @@
         <v>36</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N51" s="2">
         <v>0</v>
@@ -7476,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R51" s="3">
         <v>8</v>
@@ -7488,10 +7492,10 @@
         <v>45832</v>
       </c>
       <c r="U51" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="V51" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="W51" s="4">
         <v>45693</v>
@@ -7500,7 +7504,7 @@
         <v>6</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Z51" s="2">
         <v>446</v>
@@ -7518,7 +7522,7 @@
         <v>45710</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>2016</v>
       </c>
@@ -7529,16 +7533,16 @@
         <v>78</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>35</v>
@@ -7580,7 +7584,7 @@
         <v>45715</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>75</v>
@@ -7592,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Z52" s="2">
         <v>672</v>
@@ -7610,7 +7614,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>2016</v>
       </c>
@@ -7618,19 +7622,19 @@
         <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>35</v>
@@ -7669,25 +7673,25 @@
         <v>39</v>
       </c>
       <c r="T53" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="U53" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="U53" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="V53" s="2">
         <v>0</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X53" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Y53" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="Z53" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="Z53" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="AA53" s="2">
         <v>0</v>
@@ -7696,13 +7700,13 @@
         <v>82</v>
       </c>
       <c r="AC53" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AD53" s="4">
         <v>45859</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>2016</v>
       </c>
@@ -7710,19 +7714,19 @@
         <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>35</v>
@@ -7740,7 +7744,7 @@
         <v>36</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N54" s="2">
         <v>0</v>
@@ -7764,10 +7768,10 @@
         <v>45720</v>
       </c>
       <c r="U54" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V54" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>40</v>
@@ -7776,7 +7780,7 @@
         <v>7</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Z54" s="2">
         <v>197</v>
@@ -7788,13 +7792,13 @@
         <v>39</v>
       </c>
       <c r="AC54" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AD54" s="4">
         <v>45795</v>
       </c>
     </row>
-    <row r="55" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>2016</v>
       </c>
@@ -7802,19 +7806,19 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>35</v>
@@ -7832,7 +7836,7 @@
         <v>36</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>63</v>
@@ -7856,10 +7860,10 @@
         <v>45761</v>
       </c>
       <c r="U55" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="V55" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="V55" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>49</v>
@@ -7868,7 +7872,7 @@
         <v>3</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Z55" s="2">
         <v>261</v>
@@ -7886,7 +7890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>2016</v>
       </c>
@@ -7894,19 +7898,19 @@
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>35</v>
@@ -7936,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R56" s="3">
         <v>2</v>
@@ -7945,10 +7949,10 @@
         <v>0</v>
       </c>
       <c r="T56" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="U56" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="U56" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="V56" s="2" t="s">
         <v>39</v>
@@ -7960,10 +7964,10 @@
         <v>43</v>
       </c>
       <c r="Y56" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z56" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="Z56" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="AA56" s="4">
         <v>45710</v>
@@ -7978,7 +7982,7 @@
         <v>45711</v>
       </c>
     </row>
-    <row r="57" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>2016</v>
       </c>
@@ -7986,19 +7990,19 @@
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>35</v>
@@ -8034,13 +8038,13 @@
         <v>1</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T57" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="U57" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="U57" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>75</v>
@@ -8052,16 +8056,16 @@
         <v>0</v>
       </c>
       <c r="Y57" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="Z57" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="Z57" s="2" t="s">
+      <c r="AA57" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB57" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="AA57" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB57" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="AC57" s="2">
         <v>544</v>
@@ -8070,7 +8074,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="58" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>2016</v>
       </c>
@@ -8078,19 +8082,19 @@
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>35</v>
@@ -8108,7 +8112,7 @@
         <v>36</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N58" s="2">
         <v>0</v>
@@ -8132,10 +8136,10 @@
         <v>45811</v>
       </c>
       <c r="U58" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="V58" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="V58" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="W58" s="2" t="s">
         <v>39</v>
@@ -8162,7 +8166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>2016</v>
       </c>
@@ -8170,7 +8174,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>32</v>
@@ -8182,7 +8186,7 @@
         <v>32</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>35</v>
@@ -8221,10 +8225,10 @@
         <v>65</v>
       </c>
       <c r="T59" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="U59" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="V59" s="2">
         <v>0</v>
@@ -8236,10 +8240,10 @@
         <v>65</v>
       </c>
       <c r="Y59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="Z59" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="Z59" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="AA59" s="2">
         <v>0</v>
@@ -8254,7 +8258,7 @@
         <v>45862</v>
       </c>
     </row>
-    <row r="60" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>2016</v>
       </c>
@@ -8262,7 +8266,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>32</v>
@@ -8274,7 +8278,7 @@
         <v>32</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>35</v>
@@ -8328,10 +8332,10 @@
         <v>2</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z60" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA60" s="4">
         <v>45784</v>
@@ -8346,7 +8350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>2016</v>
       </c>
@@ -8354,10 +8358,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>113</v>
@@ -8366,7 +8370,7 @@
         <v>113</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>35</v>
@@ -8408,7 +8412,7 @@
         <v>45765</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="V61" s="2" t="s">
         <v>105</v>
@@ -8420,10 +8424,10 @@
         <v>3</v>
       </c>
       <c r="Y61" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z61" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="Z61" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="AA61" s="2">
         <v>32</v>
@@ -8438,7 +8442,7 @@
         <v>45832</v>
       </c>
     </row>
-    <row r="62" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>2016</v>
       </c>
@@ -8449,16 +8453,16 @@
         <v>32</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>35</v>
@@ -8488,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R62" s="3">
         <v>1</v>
@@ -8500,7 +8504,7 @@
         <v>45721</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="V62" s="2">
         <v>0</v>
@@ -8512,10 +8516,10 @@
         <v>3</v>
       </c>
       <c r="Y62" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z62" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="Z62" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="AA62" s="2">
         <v>2</v>
@@ -8530,7 +8534,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="63" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>2016</v>
       </c>
@@ -8541,16 +8545,16 @@
         <v>32</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>113</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>35</v>
@@ -8592,10 +8596,10 @@
         <v>45715</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="W63" s="2" t="s">
         <v>40</v>
@@ -8604,10 +8608,10 @@
         <v>4</v>
       </c>
       <c r="Y63" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="Z63" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="Z63" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="AA63" s="2">
         <v>33</v>
@@ -8622,7 +8626,7 @@
         <v>45773</v>
       </c>
     </row>
-    <row r="64" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>2016</v>
       </c>
@@ -8633,16 +8637,16 @@
         <v>113</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>35</v>
@@ -8684,10 +8688,10 @@
         <v>45721</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="W64" s="4">
         <v>45748</v>
@@ -8696,7 +8700,7 @@
         <v>4</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Z64" s="2">
         <v>302</v>
@@ -8714,7 +8718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>2016</v>
       </c>
@@ -8725,16 +8729,16 @@
         <v>113</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>35</v>
@@ -8776,10 +8780,10 @@
         <v>45791</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>107</v>
@@ -8788,7 +8792,7 @@
         <v>3</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z65" s="2">
         <v>121</v>
@@ -8806,7 +8810,7 @@
         <v>45682</v>
       </c>
     </row>
-    <row r="66" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>2016</v>
       </c>
@@ -8814,19 +8818,19 @@
         <v>65</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>35</v>
@@ -8844,7 +8848,7 @@
         <v>36</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N66" s="2">
         <v>0</v>
@@ -8856,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R66" s="2">
         <v>0</v>
@@ -8871,7 +8875,7 @@
         <v>125</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W66" s="2">
         <v>1</v>
@@ -8898,7 +8902,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="67" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>2016</v>
       </c>
@@ -8906,19 +8910,19 @@
         <v>66</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F67" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>35</v>
@@ -8936,7 +8940,7 @@
         <v>36</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N67" s="2">
         <v>0</v>
@@ -8960,10 +8964,10 @@
         <v>45787</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="W67" s="4">
         <v>45809</v>
@@ -8975,7 +8979,7 @@
         <v>45907</v>
       </c>
       <c r="Z67" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AA67" s="4">
         <v>45701</v>
@@ -8990,7 +8994,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="68" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>2016</v>
       </c>
@@ -8998,19 +9002,19 @@
         <v>67</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>35</v>
@@ -9028,7 +9032,7 @@
         <v>36</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N68" s="2">
         <v>0</v>
@@ -9052,7 +9056,7 @@
         <v>45842</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V68" s="2" t="s">
         <v>39</v>
@@ -9064,10 +9068,10 @@
         <v>1</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z68" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AA68" s="2">
         <v>3</v>
@@ -9082,7 +9086,7 @@
         <v>45767</v>
       </c>
     </row>
-    <row r="69" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>2016</v>
       </c>
@@ -9090,19 +9094,19 @@
         <v>68</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F69" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>35</v>
@@ -9144,7 +9148,7 @@
         <v>45764</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>75</v>
@@ -9159,7 +9163,7 @@
         <v>45755</v>
       </c>
       <c r="Z69" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AA69" s="2">
         <v>82</v>
@@ -9174,7 +9178,7 @@
         <v>45795</v>
       </c>
     </row>
-    <row r="70" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>2016</v>
       </c>
@@ -9182,10 +9186,10 @@
         <v>69</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>86</v>
@@ -9194,7 +9198,7 @@
         <v>86</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>35</v>
@@ -9224,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R70" s="3">
         <v>1</v>
@@ -9236,7 +9240,7 @@
         <v>45694</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="V70" s="2">
         <v>0</v>
@@ -9248,10 +9252,10 @@
         <v>6</v>
       </c>
       <c r="Y70" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="Z70" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="Z70" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="AA70" s="2">
         <v>4</v>
@@ -9266,7 +9270,7 @@
         <v>45923</v>
       </c>
     </row>
-    <row r="71" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>2016</v>
       </c>
@@ -9274,7 +9278,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>59</v>
@@ -9286,7 +9290,7 @@
         <v>59</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>35</v>
@@ -9304,7 +9308,7 @@
         <v>36</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N71" s="2">
         <v>0</v>
@@ -9328,7 +9332,7 @@
         <v>45780</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>123</v>
@@ -9343,7 +9347,7 @@
         <v>45998</v>
       </c>
       <c r="Z71" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AA71" s="4">
         <v>45840</v>
@@ -9358,7 +9362,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="72" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>2016</v>
       </c>
@@ -9369,16 +9373,16 @@
         <v>86</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>35</v>
@@ -9396,7 +9400,7 @@
         <v>36</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>65</v>
@@ -9420,7 +9424,7 @@
         <v>45666</v>
       </c>
       <c r="U72" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>40</v>
@@ -9432,10 +9436,10 @@
         <v>4</v>
       </c>
       <c r="Y72" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z72" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="Z72" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="AA72" s="2">
         <v>10</v>
@@ -9450,7 +9454,7 @@
         <v>45831</v>
       </c>
     </row>
-    <row r="73" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>2016</v>
       </c>
@@ -9461,13 +9465,13 @@
         <v>86</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>53</v>
@@ -9512,7 +9516,7 @@
         <v>45719</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="V73" s="2" t="s">
         <v>39</v>
@@ -9524,10 +9528,10 @@
         <v>3</v>
       </c>
       <c r="Y73" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Z73" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AA73" s="4">
         <v>45902</v>
@@ -9542,7 +9546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>2016</v>
       </c>
@@ -9553,13 +9557,13 @@
         <v>59</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>53</v>
@@ -9580,10 +9584,10 @@
         <v>36</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>104</v>
@@ -9592,7 +9596,7 @@
         <v>5</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="R74" s="2" t="s">
         <v>74</v>
@@ -9604,16 +9608,16 @@
         <v>45844</v>
       </c>
       <c r="U74" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="V74" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="W74" s="4">
         <v>45748</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y74" s="4">
         <v>45754</v>
@@ -9634,7 +9638,7 @@
         <v>45713</v>
       </c>
     </row>
-    <row r="75" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>2016</v>
       </c>
@@ -9645,16 +9649,16 @@
         <v>59</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>35</v>
@@ -9693,10 +9697,10 @@
         <v>65</v>
       </c>
       <c r="T75" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="U75" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="U75" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="V75" s="2" t="s">
         <v>49</v>
@@ -9711,7 +9715,7 @@
         <v>8</v>
       </c>
       <c r="Z75" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA75" s="4">
         <v>45852</v>
@@ -9726,7 +9730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>2016</v>
       </c>
@@ -9734,19 +9738,19 @@
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>94</v>
       </c>
       <c r="F76" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>35</v>
@@ -9767,7 +9771,7 @@
         <v>75</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O76" s="2">
         <v>0</v>
@@ -9785,7 +9789,7 @@
         <v>39</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="U76" s="2" t="s">
         <v>125</v>
@@ -9800,10 +9804,10 @@
         <v>6</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Z76" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AA76" s="2">
         <v>0</v>
@@ -9812,13 +9816,13 @@
         <v>39</v>
       </c>
       <c r="AC76" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AD76" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>2016</v>
       </c>
@@ -9826,19 +9830,19 @@
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D77" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>35</v>
@@ -9856,7 +9860,7 @@
         <v>36</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N77" s="2">
         <v>0</v>
@@ -9880,7 +9884,7 @@
         <v>45685</v>
       </c>
       <c r="U77" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="V77" s="5">
         <v>45717</v>
@@ -9892,7 +9896,7 @@
         <v>216</v>
       </c>
       <c r="Y77" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z77" s="2">
         <v>993</v>
@@ -9910,7 +9914,7 @@
         <v>45711</v>
       </c>
     </row>
-    <row r="78" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>2016</v>
       </c>
@@ -9918,19 +9922,19 @@
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>35</v>
@@ -9969,13 +9973,13 @@
         <v>0</v>
       </c>
       <c r="T78" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="U78" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="U78" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="V78" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W78" s="2" t="s">
         <v>104</v>
@@ -10002,7 +10006,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="79" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>2016</v>
       </c>
@@ -10010,10 +10014,10 @@
         <v>78</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>94</v>
@@ -10022,7 +10026,7 @@
         <v>94</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>35</v>
@@ -10061,10 +10065,10 @@
         <v>39</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="U79" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="V79" s="2">
         <v>0</v>
@@ -10079,7 +10083,7 @@
         <v>45695</v>
       </c>
       <c r="Z79" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AA79" s="2">
         <v>0</v>
@@ -10094,7 +10098,7 @@
         <v>45914</v>
       </c>
     </row>
-    <row r="80" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>2016</v>
       </c>
@@ -10105,16 +10109,16 @@
         <v>94</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="G80" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>35</v>
@@ -10153,22 +10157,22 @@
         <v>0</v>
       </c>
       <c r="T80" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="U80" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>82</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X80" s="2">
         <v>0</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Z80" s="2">
         <v>895</v>
@@ -10186,7 +10190,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="81" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>2016</v>
       </c>
@@ -10197,16 +10201,16 @@
         <v>94</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>35</v>
@@ -10224,7 +10228,7 @@
         <v>36</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>65</v>
@@ -10245,13 +10249,13 @@
         <v>0</v>
       </c>
       <c r="T81" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="U81" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="U81" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="V81" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W81" s="2">
         <v>1</v>
@@ -10278,7 +10282,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="82" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>2016</v>
       </c>
@@ -10286,19 +10290,19 @@
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>35</v>
@@ -10340,7 +10344,7 @@
         <v>45659</v>
       </c>
       <c r="U82" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>84</v>
@@ -10355,7 +10359,7 @@
         <v>45844</v>
       </c>
       <c r="Z82" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AA82" s="2">
         <v>4</v>
@@ -10370,7 +10374,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="83" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>2016</v>
       </c>
@@ -10378,19 +10382,19 @@
         <v>82</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>35</v>
@@ -10408,7 +10412,7 @@
         <v>36</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N83" s="2">
         <v>0</v>
@@ -10432,7 +10436,7 @@
         <v>45689</v>
       </c>
       <c r="U83" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>82</v>
@@ -10447,7 +10451,7 @@
         <v>45723</v>
       </c>
       <c r="Z83" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AA83" s="4">
         <v>45664</v>
@@ -10462,7 +10466,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="84" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>2016</v>
       </c>
@@ -10470,19 +10474,19 @@
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>35</v>
@@ -10524,7 +10528,7 @@
         <v>45840</v>
       </c>
       <c r="U84" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V84" s="2">
         <v>0</v>
@@ -10539,7 +10543,7 @@
         <v>45665</v>
       </c>
       <c r="Z84" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AA84" s="2">
         <v>24</v>
@@ -10554,7 +10558,7 @@
         <v>45679</v>
       </c>
     </row>
-    <row r="85" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>2016</v>
       </c>
@@ -10562,19 +10566,19 @@
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>35</v>
@@ -10616,13 +10620,13 @@
         <v>45904</v>
       </c>
       <c r="U85" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="V85" s="2" t="s">
         <v>82</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X85" s="3">
         <v>4</v>
@@ -10631,7 +10635,7 @@
         <v>45696</v>
       </c>
       <c r="Z85" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AA85" s="4">
         <v>45726</v>
@@ -10646,7 +10650,7 @@
         <v>45797</v>
       </c>
     </row>
-    <row r="86" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>2016</v>
       </c>
@@ -10654,19 +10658,19 @@
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>35</v>
@@ -10684,7 +10688,7 @@
         <v>36</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N86" s="2">
         <v>0</v>
@@ -10708,10 +10712,10 @@
         <v>45660</v>
       </c>
       <c r="U86" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="V86" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="V86" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="W86" s="2">
         <v>0</v>
@@ -10723,7 +10727,7 @@
         <v>45785</v>
       </c>
       <c r="Z86" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AA86" s="2">
         <v>0</v>
@@ -10738,7 +10742,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="87" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>2016</v>
       </c>
@@ -10746,19 +10750,19 @@
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G87" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>35</v>
@@ -10800,7 +10804,7 @@
         <v>45906</v>
       </c>
       <c r="U87" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="V87" s="2" t="s">
         <v>40</v>
@@ -10815,7 +10819,7 @@
         <v>45969</v>
       </c>
       <c r="Z87" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA87" s="4">
         <v>45665</v>
@@ -10830,7 +10834,7 @@
         <v>45893</v>
       </c>
     </row>
-    <row r="88" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>2016</v>
       </c>
@@ -10838,19 +10842,19 @@
         <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="G88" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>35</v>
@@ -10892,10 +10896,10 @@
         <v>45779</v>
       </c>
       <c r="U88" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="W88" s="2">
         <v>0</v>
@@ -10907,7 +10911,7 @@
         <v>45696</v>
       </c>
       <c r="Z88" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AA88" s="2">
         <v>0</v>
@@ -10922,7 +10926,7 @@
         <v>45921</v>
       </c>
     </row>
-    <row r="89" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>2016</v>
       </c>
@@ -10930,19 +10934,19 @@
         <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="F89" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>522</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>35</v>
@@ -10984,10 +10988,10 @@
         <v>45826</v>
       </c>
       <c r="U89" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="W89" s="2">
         <v>1</v>
@@ -11014,7 +11018,7 @@
         <v>45764</v>
       </c>
     </row>
-    <row r="90" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>2016</v>
       </c>
@@ -11022,19 +11026,19 @@
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="F90" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="G90" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>35</v>
@@ -11076,7 +11080,7 @@
         <v>45748</v>
       </c>
       <c r="U90" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="V90" s="2" t="s">
         <v>40</v>
@@ -11100,13 +11104,13 @@
         <v>0</v>
       </c>
       <c r="AC90" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AD90" s="4">
         <v>45763</v>
       </c>
     </row>
-    <row r="91" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>2016</v>
       </c>
@@ -11114,19 +11118,19 @@
         <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>35</v>
@@ -11165,10 +11169,10 @@
         <v>39</v>
       </c>
       <c r="T91" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="U91" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="U91" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="V91" s="2">
         <v>0</v>
@@ -11186,7 +11190,7 @@
         <v>174</v>
       </c>
       <c r="AA91" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AB91" s="2" t="s">
         <v>39</v>
@@ -11198,7 +11202,7 @@
         <v>45686</v>
       </c>
     </row>
-    <row r="92" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>2016</v>
       </c>
@@ -11209,16 +11213,16 @@
         <v>52</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>35</v>
@@ -11257,10 +11261,10 @@
         <v>39</v>
       </c>
       <c r="T92" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="U92" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="U92" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="V92" s="2">
         <v>0</v>
@@ -11278,7 +11282,7 @@
         <v>198</v>
       </c>
       <c r="AA92" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AB92" s="2" t="s">
         <v>39</v>
@@ -11290,7 +11294,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="93" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>2016</v>
       </c>
@@ -11301,16 +11305,16 @@
         <v>52</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G93" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>35</v>
@@ -11352,10 +11356,10 @@
         <v>45815</v>
       </c>
       <c r="U93" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="W93" s="4">
         <v>45658</v>
@@ -11364,10 +11368,10 @@
         <v>4</v>
       </c>
       <c r="Y93" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="Z93" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="Z93" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="AA93" s="2">
         <v>7</v>
@@ -11382,7 +11386,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="94" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>2016</v>
       </c>
@@ -11390,19 +11394,19 @@
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="G94" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>543</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>35</v>
@@ -11420,7 +11424,7 @@
         <v>36</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N94" s="2">
         <v>0</v>
@@ -11444,7 +11448,7 @@
         <v>45750</v>
       </c>
       <c r="U94" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="V94" s="2">
         <v>0</v>
@@ -11474,7 +11478,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="95" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>2016</v>
       </c>
@@ -11482,19 +11486,19 @@
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>35</v>
@@ -11524,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="R95" s="3">
         <v>6</v>
@@ -11536,10 +11540,10 @@
         <v>45720</v>
       </c>
       <c r="U95" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="W95" s="2" t="s">
         <v>77</v>
@@ -11566,7 +11570,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>2016</v>
       </c>
@@ -11574,19 +11578,19 @@
         <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>35</v>
@@ -11628,7 +11632,7 @@
         <v>45875</v>
       </c>
       <c r="U96" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="V96" s="2">
         <v>0</v>
@@ -11640,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Z96" s="2">
         <v>236</v>
@@ -11658,7 +11662,7 @@
         <v>45832</v>
       </c>
     </row>
-    <row r="97" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>2016</v>
       </c>
@@ -11666,19 +11670,19 @@
         <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="G97" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>554</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>35</v>
@@ -11720,10 +11724,10 @@
         <v>45663</v>
       </c>
       <c r="U97" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>40</v>
@@ -11735,7 +11739,7 @@
         <v>45784</v>
       </c>
       <c r="Z97" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AA97" s="4">
         <v>45756</v>
@@ -11750,7 +11754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>2016</v>
       </c>
@@ -11758,19 +11762,19 @@
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>119</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>558</v>
+        <v>832</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>35</v>
@@ -11812,13 +11816,13 @@
         <v>45695</v>
       </c>
       <c r="U98" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="V98" s="2">
         <v>0</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X98" s="2" t="s">
         <v>65</v>
@@ -11827,7 +11831,7 @@
         <v>45815</v>
       </c>
       <c r="Z98" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AA98" s="4">
         <v>45781</v>
@@ -11842,7 +11846,7 @@
         <v>45896</v>
       </c>
     </row>
-    <row r="99" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>2016</v>
       </c>
@@ -11850,19 +11854,19 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>35</v>
@@ -11904,7 +11908,7 @@
         <v>45841</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>63</v>
@@ -11916,10 +11920,10 @@
         <v>3</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="Z99" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AA99" s="4">
         <v>45665</v>
@@ -11934,7 +11938,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="100" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>2016</v>
       </c>
@@ -11942,19 +11946,19 @@
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>119</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>35</v>
@@ -11993,10 +11997,10 @@
         <v>0</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>82</v>
@@ -12008,7 +12012,7 @@
         <v>8</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Z100" s="2">
         <v>139</v>
@@ -12026,7 +12030,7 @@
         <v>45806</v>
       </c>
     </row>
-    <row r="101" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>2016</v>
       </c>
@@ -12034,19 +12038,19 @@
         <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>62</v>
@@ -12085,13 +12089,13 @@
         <v>45809</v>
       </c>
       <c r="T101" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="W101" s="4">
         <v>45694</v>
@@ -12118,7 +12122,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="102" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>2016</v>
       </c>
@@ -12129,16 +12133,16 @@
         <v>119</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G102" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>35</v>
@@ -12177,13 +12181,13 @@
         <v>105</v>
       </c>
       <c r="T102" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="W102" s="4">
         <v>45780</v>
@@ -12192,7 +12196,7 @@
         <v>5</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Z102" s="2">
         <v>721</v>
@@ -12210,7 +12214,7 @@
         <v>45836</v>
       </c>
     </row>
-    <row r="103" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>2016</v>
       </c>
@@ -12221,16 +12225,16 @@
         <v>119</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>35</v>
@@ -12260,22 +12264,22 @@
         <v>0</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R103" s="3">
         <v>3</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T103" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="V103" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="U103" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="V103" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="W103" s="4">
         <v>45842</v>
@@ -12284,7 +12288,7 @@
         <v>6</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z103" s="2">
         <v>755</v>
@@ -12302,7 +12306,7 @@
         <v>45832</v>
       </c>
     </row>
-    <row r="104" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>2016</v>
       </c>
@@ -12310,19 +12314,19 @@
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>35</v>
@@ -12340,7 +12344,7 @@
         <v>36</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N104" s="2">
         <v>0</v>
@@ -12364,10 +12368,10 @@
         <v>45906</v>
       </c>
       <c r="U104" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="W104" s="4">
         <v>45749</v>
@@ -12376,10 +12380,10 @@
         <v>65</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Z104" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AA104" s="2">
         <v>3</v>
@@ -12388,13 +12392,13 @@
         <v>0</v>
       </c>
       <c r="AC104" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AD104" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>2016</v>
       </c>
@@ -12402,19 +12406,19 @@
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>35</v>
@@ -12444,22 +12448,22 @@
         <v>0</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R105" s="2">
         <v>0</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T105" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="U105" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="V105" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="U105" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="V105" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="W105" s="4">
         <v>45750</v>
@@ -12468,7 +12472,7 @@
         <v>4</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Z105" s="2">
         <v>720</v>
@@ -12486,7 +12490,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="106" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>2016</v>
       </c>
@@ -12494,19 +12498,19 @@
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>35</v>
@@ -12548,10 +12552,10 @@
         <v>45764</v>
       </c>
       <c r="U106" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="V106" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>65</v>
@@ -12560,7 +12564,7 @@
         <v>2</v>
       </c>
       <c r="Y106" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="Z106" s="2">
         <v>96</v>
@@ -12578,7 +12582,7 @@
         <v>45679</v>
       </c>
     </row>
-    <row r="107" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>2016</v>
       </c>
@@ -12586,19 +12590,19 @@
         <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="G107" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>606</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>35</v>
@@ -12637,13 +12641,13 @@
         <v>74</v>
       </c>
       <c r="T107" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="U107" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="W107" s="4">
         <v>45778</v>
@@ -12670,7 +12674,7 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="108" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>2016</v>
       </c>
@@ -12678,19 +12682,19 @@
         <v>107</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>611</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>35</v>
@@ -12708,7 +12712,7 @@
         <v>36</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N108" s="2">
         <v>0</v>
@@ -12732,7 +12736,7 @@
         <v>5</v>
       </c>
       <c r="U108" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="V108" s="2" t="s">
         <v>75</v>
@@ -12744,10 +12748,10 @@
         <v>7</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="Z108" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AA108" s="2">
         <v>1</v>
@@ -12756,13 +12760,13 @@
         <v>0</v>
       </c>
       <c r="AC108" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AD108" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>2016</v>
       </c>
@@ -12770,19 +12774,19 @@
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>35</v>
@@ -12821,16 +12825,16 @@
         <v>0</v>
       </c>
       <c r="T109" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="U109" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="W109" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X109" s="2">
         <v>0</v>
@@ -12854,7 +12858,7 @@
         <v>45776</v>
       </c>
     </row>
-    <row r="110" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>2016</v>
       </c>
@@ -12862,19 +12866,19 @@
         <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>35</v>
@@ -12913,13 +12917,13 @@
         <v>67</v>
       </c>
       <c r="T110" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="U110" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W110" s="2">
         <v>0</v>
@@ -12928,13 +12932,13 @@
         <v>1</v>
       </c>
       <c r="Y110" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="Z110" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AA110" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AB110" s="2" t="s">
         <v>43</v>
@@ -12946,7 +12950,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="111" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>2016</v>
       </c>
@@ -12954,19 +12958,19 @@
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>35</v>
@@ -13002,16 +13006,16 @@
         <v>2</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T111" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="U111" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W111" s="2">
         <v>0</v>
@@ -13023,10 +13027,10 @@
         <v>45694</v>
       </c>
       <c r="Z111" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AA111" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AB111" s="2" t="s">
         <v>67</v>
@@ -13038,7 +13042,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="112" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>2016</v>
       </c>
@@ -13046,19 +13050,19 @@
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D112" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>632</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>35</v>
@@ -13097,13 +13101,13 @@
         <v>39</v>
       </c>
       <c r="T112" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="U112" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="V112" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="U112" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="V112" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>75</v>
@@ -13112,7 +13116,7 @@
         <v>37</v>
       </c>
       <c r="Y112" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Z112" s="2">
         <v>295</v>
@@ -13130,7 +13134,7 @@
         <v>45771</v>
       </c>
     </row>
-    <row r="113" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>2016</v>
       </c>
@@ -13138,19 +13142,19 @@
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>636</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>638</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>35</v>
@@ -13189,13 +13193,13 @@
         <v>82</v>
       </c>
       <c r="T113" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="U113" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W113" s="2" t="s">
         <v>104</v>
@@ -13222,7 +13226,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="114" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>2016</v>
       </c>
@@ -13230,19 +13234,19 @@
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>643</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>35</v>
@@ -13281,13 +13285,13 @@
         <v>39</v>
       </c>
       <c r="T114" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="U114" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="W114" s="4">
         <v>45905</v>
@@ -13296,7 +13300,7 @@
         <v>7</v>
       </c>
       <c r="Y114" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z114" s="2">
         <v>663</v>
@@ -13314,7 +13318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>2016</v>
       </c>
@@ -13322,19 +13326,19 @@
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>35</v>
@@ -13352,19 +13356,19 @@
         <v>36</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>63</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P115" s="2">
         <v>0</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R115" s="3">
         <v>3</v>
@@ -13373,13 +13377,13 @@
         <v>39</v>
       </c>
       <c r="T115" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="U115" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="W115" s="4">
         <v>45691</v>
@@ -13388,7 +13392,7 @@
         <v>22</v>
       </c>
       <c r="Y115" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z115" s="2">
         <v>458</v>
@@ -13406,7 +13410,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="116" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>2016</v>
       </c>
@@ -13414,19 +13418,19 @@
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>35</v>
@@ -13465,10 +13469,10 @@
         <v>0</v>
       </c>
       <c r="T116" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="U116" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="V116" s="2" t="s">
         <v>82</v>
@@ -13498,7 +13502,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="117" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>2016</v>
       </c>
@@ -13506,7 +13510,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>100</v>
@@ -13518,7 +13522,7 @@
         <v>100</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>35</v>
@@ -13560,7 +13564,7 @@
         <v>45753</v>
       </c>
       <c r="U117" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="V117" s="2" t="s">
         <v>82</v>
@@ -13590,7 +13594,7 @@
         <v>45893</v>
       </c>
     </row>
-    <row r="118" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>2016</v>
       </c>
@@ -13598,7 +13602,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>100</v>
@@ -13610,7 +13614,7 @@
         <v>100</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>35</v>
@@ -13652,10 +13656,10 @@
         <v>45875</v>
       </c>
       <c r="U118" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="W118" s="4">
         <v>45658</v>
@@ -13667,10 +13671,10 @@
         <v>45906</v>
       </c>
       <c r="Z118" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="AA118" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AB118" s="2" t="s">
         <v>63</v>
@@ -13682,7 +13686,7 @@
         <v>45892</v>
       </c>
     </row>
-    <row r="119" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>2016</v>
       </c>
@@ -13690,19 +13694,19 @@
         <v>118</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>35</v>
@@ -13741,13 +13745,13 @@
         <v>0</v>
       </c>
       <c r="T119" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="U119" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="W119" s="4">
         <v>45902</v>
@@ -13756,7 +13760,7 @@
         <v>5</v>
       </c>
       <c r="Y119" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="Z119" s="2">
         <v>297</v>
@@ -13774,7 +13778,7 @@
         <v>45889</v>
       </c>
     </row>
-    <row r="120" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>2016</v>
       </c>
@@ -13782,19 +13786,19 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>35</v>
@@ -13836,10 +13840,10 @@
         <v>2</v>
       </c>
       <c r="U120" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="W120" s="4">
         <v>45872</v>
@@ -13866,7 +13870,7 @@
         <v>45773</v>
       </c>
     </row>
-    <row r="121" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>2016</v>
       </c>
@@ -13874,19 +13878,19 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>35</v>
@@ -13916,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R121" s="3">
         <v>1</v>
@@ -13928,19 +13932,19 @@
         <v>45718</v>
       </c>
       <c r="U121" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W121" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X121" s="3">
         <v>4</v>
       </c>
       <c r="Y121" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="Z121" s="4">
         <v>45716</v>
@@ -13952,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="AC121" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="AD121" s="4">
         <v>45677</v>
       </c>
     </row>
-    <row r="122" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>2016</v>
       </c>
@@ -13966,19 +13970,19 @@
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>667</v>
+        <v>113</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>35</v>
@@ -14020,19 +14024,19 @@
         <v>16</v>
       </c>
       <c r="U122" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W122" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X122" s="3">
         <v>4</v>
       </c>
       <c r="Y122" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="Z122" s="4">
         <v>45713</v>
@@ -14050,7 +14054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>2016</v>
       </c>
@@ -14058,19 +14062,19 @@
         <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D123" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="G123" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>678</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>35</v>
@@ -14088,7 +14092,7 @@
         <v>36</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N123" s="2">
         <v>0</v>
@@ -14112,10 +14116,10 @@
         <v>8</v>
       </c>
       <c r="U123" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="V123" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="W123" s="2" t="s">
         <v>75</v>
@@ -14124,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="Y123" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z123" s="2">
         <v>150</v>
@@ -14142,7 +14146,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>2016</v>
       </c>
@@ -14150,19 +14154,19 @@
         <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D124" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>681</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>683</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>35</v>
@@ -14198,16 +14202,16 @@
         <v>1</v>
       </c>
       <c r="S124" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T124" s="4">
         <v>45855</v>
       </c>
       <c r="U124" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="V124" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="W124" s="2">
         <v>0</v>
@@ -14216,7 +14220,7 @@
         <v>3</v>
       </c>
       <c r="Y124" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="Z124" s="2">
         <v>326</v>
@@ -14234,7 +14238,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="125" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>2016</v>
       </c>
@@ -14242,19 +14246,19 @@
         <v>124</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>35</v>
@@ -14272,7 +14276,7 @@
         <v>36</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N125" s="2">
         <v>0</v>
@@ -14296,19 +14300,19 @@
         <v>45673</v>
       </c>
       <c r="U125" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="V125" s="2" t="s">
         <v>104</v>
       </c>
       <c r="W125" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X125" s="3">
         <v>15</v>
       </c>
       <c r="Y125" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="Z125" s="2">
         <v>202</v>
@@ -14323,10 +14327,10 @@
         <v>402</v>
       </c>
       <c r="AD125" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="126" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>2016</v>
       </c>
@@ -14334,19 +14338,19 @@
         <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>35</v>
@@ -14388,7 +14392,7 @@
         <v>45683</v>
       </c>
       <c r="U126" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="V126" s="2" t="s">
         <v>84</v>
@@ -14403,7 +14407,7 @@
         <v>7</v>
       </c>
       <c r="Z126" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AA126" s="4">
         <v>45784</v>
@@ -14418,7 +14422,7 @@
         <v>45890</v>
       </c>
     </row>
-    <row r="127" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>2016</v>
       </c>
@@ -14426,16 +14430,16 @@
         <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>53</v>
@@ -14480,10 +14484,10 @@
         <v>45827</v>
       </c>
       <c r="U127" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="W127" s="2">
         <v>0</v>
@@ -14492,7 +14496,7 @@
         <v>6</v>
       </c>
       <c r="Y127" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="Z127" s="2">
         <v>323</v>
@@ -14501,7 +14505,7 @@
         <v>32</v>
       </c>
       <c r="AB127" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AC127" s="2">
         <v>585</v>
@@ -14510,7 +14514,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="128" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>2016</v>
       </c>
@@ -14521,16 +14525,16 @@
         <v>70</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>35</v>
@@ -14569,16 +14573,16 @@
         <v>65</v>
       </c>
       <c r="T128" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="U128" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="V128" s="2" t="s">
         <v>40</v>
       </c>
       <c r="W128" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X128" s="2">
         <v>0</v>
@@ -14602,7 +14606,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="129" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>2016</v>
       </c>
@@ -14613,16 +14617,16 @@
         <v>70</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>35</v>
@@ -14664,7 +14668,7 @@
         <v>34</v>
       </c>
       <c r="U129" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="V129" s="2">
         <v>0</v>
@@ -14676,10 +14680,10 @@
         <v>0</v>
       </c>
       <c r="Y129" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Z129" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AA129" s="4">
         <v>45719</v>
@@ -14691,10 +14695,10 @@
         <v>309</v>
       </c>
       <c r="AD129" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
-    <row r="130" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>2016</v>
       </c>
@@ -14705,16 +14709,16 @@
         <v>70</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>35</v>
@@ -14756,7 +14760,7 @@
         <v>45864</v>
       </c>
       <c r="U130" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="V130" s="2" t="s">
         <v>75</v>
@@ -14786,7 +14790,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="131" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>2016</v>
       </c>
@@ -14794,19 +14798,19 @@
         <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>708</v>
+        <v>723</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>833</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>35</v>
@@ -14845,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="T131" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="U131" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="V131" s="4">
         <v>45689</v>
@@ -14863,7 +14867,7 @@
         <v>45844</v>
       </c>
       <c r="Z131" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AA131" s="4">
         <v>45906</v>
@@ -14878,7 +14882,7 @@
         <v>45739</v>
       </c>
     </row>
-    <row r="132" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>2016</v>
       </c>
@@ -14886,19 +14890,19 @@
         <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D132" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>716</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>35</v>
@@ -14940,7 +14944,7 @@
         <v>45757</v>
       </c>
       <c r="U132" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="V132" s="4">
         <v>45717</v>
@@ -14952,13 +14956,13 @@
         <v>63</v>
       </c>
       <c r="Y132" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="Z132" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AA132" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AB132" s="2">
         <v>0</v>
@@ -14970,7 +14974,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="133" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>2016</v>
       </c>
@@ -14978,19 +14982,19 @@
         <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>35</v>
@@ -15032,7 +15036,7 @@
         <v>45724</v>
       </c>
       <c r="U133" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="V133" s="2" t="s">
         <v>77</v>
@@ -15044,13 +15048,13 @@
         <v>75</v>
       </c>
       <c r="Y133" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Z133" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AA133" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AB133" s="2" t="s">
         <v>39</v>
@@ -15062,7 +15066,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="134" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>2016</v>
       </c>
@@ -15070,19 +15074,19 @@
         <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F134" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="G134" s="1" t="s">
         <v>727</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>729</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>35</v>
@@ -15100,7 +15104,7 @@
         <v>36</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N134" s="2">
         <v>0</v>
@@ -15112,7 +15116,7 @@
         <v>65</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R134" s="3">
         <v>3</v>
@@ -15124,10 +15128,10 @@
         <v>45875</v>
       </c>
       <c r="U134" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="W134" s="2" t="s">
         <v>104</v>
@@ -15136,7 +15140,7 @@
         <v>0</v>
       </c>
       <c r="Y134" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z134" s="2">
         <v>355</v>
@@ -15154,7 +15158,7 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="135" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>2017</v>
       </c>
@@ -15162,19 +15166,19 @@
         <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>732</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>735</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>36</v>
@@ -15192,7 +15196,7 @@
         <v>36</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N135" s="2" t="s">
         <v>63</v>
@@ -15246,7 +15250,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="136" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>2017</v>
       </c>
@@ -15254,19 +15258,19 @@
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="G136" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>739</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>35</v>
@@ -15305,10 +15309,10 @@
         <v>0</v>
       </c>
       <c r="T136" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="U136" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="V136" s="2" t="s">
         <v>67</v>
@@ -15320,7 +15324,7 @@
         <v>2</v>
       </c>
       <c r="Y136" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="Z136" s="2">
         <v>762</v>
@@ -15338,7 +15342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="137" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>2019</v>
       </c>
@@ -15346,19 +15350,19 @@
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>35</v>
@@ -15400,7 +15404,7 @@
         <v>45858</v>
       </c>
       <c r="U137" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="V137" s="2" t="s">
         <v>39</v>
@@ -15415,7 +15419,7 @@
         <v>45784</v>
       </c>
       <c r="Z137" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="AA137" s="2">
         <v>18</v>
@@ -15424,13 +15428,13 @@
         <v>37</v>
       </c>
       <c r="AC137" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="AD137" s="4">
         <v>45675</v>
       </c>
     </row>
-    <row r="138" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>2019</v>
       </c>
@@ -15438,19 +15442,19 @@
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>35</v>
@@ -15471,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O138" s="2">
         <v>0</v>
@@ -15492,7 +15496,7 @@
         <v>45886</v>
       </c>
       <c r="U138" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="V138" s="2">
         <v>7</v>
@@ -15522,7 +15526,7 @@
         <v>45888</v>
       </c>
     </row>
-    <row r="139" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>2019</v>
       </c>
@@ -15530,19 +15534,19 @@
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>35</v>
@@ -15584,10 +15588,10 @@
         <v>45803</v>
       </c>
       <c r="U139" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V139" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="W139" s="2" t="s">
         <v>39</v>
@@ -15608,13 +15612,13 @@
         <v>67</v>
       </c>
       <c r="AC139" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AD139" s="4">
         <v>45888</v>
       </c>
     </row>
-    <row r="140" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>2019</v>
       </c>
@@ -15622,19 +15626,19 @@
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>757</v>
+        <v>830</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>62</v>
@@ -15655,7 +15659,7 @@
         <v>39</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O140" s="2" t="s">
         <v>104</v>
@@ -15670,16 +15674,16 @@
         <v>1</v>
       </c>
       <c r="S140" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="T140" s="4">
         <v>45926</v>
       </c>
       <c r="U140" s="2" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="V140" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W140" s="2">
         <v>0</v>
@@ -15688,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="Y140" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="Z140" s="2">
         <v>361</v>
@@ -15697,7 +15701,7 @@
         <v>80</v>
       </c>
       <c r="AB140" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AC140" s="2">
         <v>509</v>
@@ -15706,7 +15710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>2019</v>
       </c>
@@ -15714,19 +15718,19 @@
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D141" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="G141" s="1" t="s">
         <v>756</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>760</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>62</v>
@@ -15762,13 +15766,13 @@
         <v>2</v>
       </c>
       <c r="S141" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="T141" s="4">
         <v>45743</v>
       </c>
       <c r="U141" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="V141" s="2" t="s">
         <v>49</v>
@@ -15777,10 +15781,10 @@
         <v>82</v>
       </c>
       <c r="X141" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="Y141" s="2" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="Z141" s="2">
         <v>279</v>
@@ -15789,7 +15793,7 @@
         <v>84</v>
       </c>
       <c r="AB141" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AC141" s="2">
         <v>551</v>
@@ -15798,7 +15802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>2019</v>
       </c>
@@ -15806,19 +15810,19 @@
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>766</v>
+        <v>159</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>62</v>
@@ -15839,7 +15843,7 @@
         <v>40</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O142" s="2" t="s">
         <v>104</v>
@@ -15854,16 +15858,16 @@
         <v>1</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="T142" s="4">
         <v>45804</v>
       </c>
       <c r="U142" s="2" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="V142" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W142" s="2" t="s">
         <v>82</v>
@@ -15872,7 +15876,7 @@
         <v>2</v>
       </c>
       <c r="Y142" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Z142" s="2">
         <v>344</v>
@@ -15884,13 +15888,13 @@
         <v>123</v>
       </c>
       <c r="AC142" s="2" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="AD142" s="4">
         <v>45891</v>
       </c>
     </row>
-    <row r="143" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>2019</v>
       </c>
@@ -15898,19 +15902,19 @@
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F143" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G143" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>771</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>62</v>
@@ -15940,31 +15944,31 @@
         <v>0</v>
       </c>
       <c r="Q143" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R143" s="3">
         <v>3</v>
       </c>
       <c r="S143" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="T143" s="4">
         <v>45745</v>
       </c>
       <c r="U143" s="2" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="V143" s="2" t="s">
         <v>49</v>
       </c>
       <c r="W143" s="2" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="X143" s="3">
         <v>9</v>
       </c>
       <c r="Y143" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Z143" s="2">
         <v>278</v>
@@ -15982,7 +15986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>2019</v>
       </c>
@@ -15990,19 +15994,19 @@
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>766</v>
+        <v>159</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>62</v>
@@ -16026,28 +16030,28 @@
         <v>134</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P144" s="2">
         <v>0</v>
       </c>
       <c r="Q144" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R144" s="3">
         <v>2</v>
       </c>
       <c r="S144" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T144" s="4">
         <v>45895</v>
       </c>
       <c r="U144" s="2" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="V144" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W144" s="4">
         <v>45658</v>
@@ -16056,7 +16060,7 @@
         <v>1</v>
       </c>
       <c r="Y144" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="Z144" s="2">
         <v>340</v>
@@ -16065,7 +16069,7 @@
         <v>80</v>
       </c>
       <c r="AB144" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AC144" s="2">
         <v>538</v>
@@ -16074,7 +16078,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="145" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>2019</v>
       </c>
@@ -16082,19 +16086,19 @@
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>766</v>
+        <v>159</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>62</v>
@@ -16112,10 +16116,10 @@
         <v>0</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O145" s="2" t="s">
         <v>104</v>
@@ -16136,7 +16140,7 @@
         <v>45797</v>
       </c>
       <c r="U145" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V145" s="2" t="s">
         <v>77</v>
@@ -16148,7 +16152,7 @@
         <v>2</v>
       </c>
       <c r="Y145" s="2" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="Z145" s="2">
         <v>374</v>
@@ -16166,7 +16170,7 @@
         <v>45771</v>
       </c>
     </row>
-    <row r="146" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>2020</v>
       </c>
@@ -16174,19 +16178,19 @@
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>35</v>
@@ -16204,7 +16208,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="N146" s="2" t="s">
         <v>63</v>
@@ -16222,28 +16226,28 @@
         <v>0</v>
       </c>
       <c r="S146" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T146" s="3">
         <v>3</v>
       </c>
       <c r="U146" s="2" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="V146" s="5">
         <v>45748</v>
       </c>
       <c r="W146" s="2" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="X146" s="2" t="s">
         <v>84</v>
       </c>
       <c r="Y146" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="Z146" s="2" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="AA146" s="2">
         <v>4</v>
@@ -16255,10 +16259,10 @@
         <v>285</v>
       </c>
       <c r="AD146" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>2021</v>
       </c>
@@ -16266,19 +16270,19 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>35</v>
@@ -16296,7 +16300,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="N147" s="2" t="s">
         <v>37</v>
@@ -16320,10 +16324,10 @@
         <v>45672</v>
       </c>
       <c r="U147" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V147" s="2" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="W147" s="2" t="s">
         <v>49</v>
@@ -16332,10 +16336,10 @@
         <v>7</v>
       </c>
       <c r="Y147" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Z147" s="2" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="AA147" s="2">
         <v>72</v>
@@ -16350,7 +16354,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="148" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>2021</v>
       </c>
@@ -16358,19 +16362,19 @@
         <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>62</v>
@@ -16412,10 +16416,10 @@
         <v>9</v>
       </c>
       <c r="U148" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V148" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W148" s="4">
         <v>45845</v>
@@ -16424,10 +16428,10 @@
         <v>6</v>
       </c>
       <c r="Y148" s="2" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="Z148" s="2" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="AA148" s="2">
         <v>2</v>
@@ -16439,10 +16443,10 @@
         <v>272</v>
       </c>
       <c r="AD148" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
-    <row r="149" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>2021</v>
       </c>
@@ -16450,19 +16454,19 @@
         <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>35</v>
@@ -16480,7 +16484,7 @@
         <v>0</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>74</v>
@@ -16492,7 +16496,7 @@
         <v>0</v>
       </c>
       <c r="Q149" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R149" s="3">
         <v>8</v>
@@ -16504,10 +16508,10 @@
         <v>45705</v>
       </c>
       <c r="U149" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V149" s="2" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="W149" s="4">
         <v>45691</v>
@@ -16516,7 +16520,7 @@
         <v>38</v>
       </c>
       <c r="Y149" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z149" s="2">
         <v>207</v>
@@ -16534,7 +16538,7 @@
         <v>45803</v>
       </c>
     </row>
-    <row r="150" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>2021</v>
       </c>
@@ -16542,19 +16546,19 @@
         <v>149</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="G150" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>798</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>35</v>
@@ -16572,7 +16576,7 @@
         <v>0</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N150" s="2">
         <v>0</v>
@@ -16590,16 +16594,16 @@
         <v>2</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T150" s="2" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="U150" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V150" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="W150" s="4">
         <v>45748</v>
@@ -16608,7 +16612,7 @@
         <v>17</v>
       </c>
       <c r="Y150" s="2" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="Z150" s="2">
         <v>196</v>
@@ -16626,7 +16630,7 @@
         <v>45802</v>
       </c>
     </row>
-    <row r="151" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>2021</v>
       </c>
@@ -16634,19 +16638,19 @@
         <v>150</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>35</v>
@@ -16682,16 +16686,16 @@
         <v>3</v>
       </c>
       <c r="S151" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T151" s="2" t="s">
         <v>137</v>
       </c>
       <c r="U151" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="V151" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="W151" s="4">
         <v>45663</v>
@@ -16700,13 +16704,13 @@
         <v>63</v>
       </c>
       <c r="Y151" s="2" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="Z151" s="4">
         <v>45683</v>
       </c>
       <c r="AA151" s="2" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="AB151" s="2">
         <v>0</v>
@@ -16718,7 +16722,7 @@
         <v>45832</v>
       </c>
     </row>
-    <row r="152" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>2022</v>
       </c>
@@ -16729,16 +16733,16 @@
         <v>119</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>35</v>
@@ -16756,10 +16760,10 @@
         <v>89</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="O152" s="2" t="s">
         <v>49</v>
@@ -16768,7 +16772,7 @@
         <v>25</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R152" s="3">
         <v>14</v>
@@ -16780,7 +16784,7 @@
         <v>45665</v>
       </c>
       <c r="U152" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="V152" s="2">
         <v>0</v>
@@ -16792,7 +16796,7 @@
         <v>53</v>
       </c>
       <c r="Y152" s="2" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="Z152" s="2">
         <v>137</v>
@@ -16810,7 +16814,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="153" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>2022</v>
       </c>
@@ -16818,19 +16822,19 @@
         <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>35</v>
@@ -16848,7 +16852,7 @@
         <v>0</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>74</v>
@@ -16869,13 +16873,13 @@
         <v>43</v>
       </c>
       <c r="T153" s="2" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="U153" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="W153" s="2" t="s">
         <v>49</v>
@@ -16884,7 +16888,7 @@
         <v>7</v>
       </c>
       <c r="Y153" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="Z153" s="2">
         <v>16</v>
@@ -16899,10 +16903,10 @@
         <v>564</v>
       </c>
       <c r="AD153" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="154" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>2022</v>
       </c>
@@ -16910,19 +16914,19 @@
         <v>153</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>35</v>
@@ -16940,7 +16944,7 @@
         <v>0</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>74</v>
@@ -16961,13 +16965,13 @@
         <v>43</v>
       </c>
       <c r="T154" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="U154" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="W154" s="2" t="s">
         <v>49</v>
@@ -16976,7 +16980,7 @@
         <v>7</v>
       </c>
       <c r="Y154" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="Z154" s="2">
         <v>16</v>
@@ -16994,7 +16998,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="155" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>2023</v>
       </c>
@@ -17002,19 +17006,19 @@
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>35</v>
@@ -17032,10 +17036,10 @@
         <v>0</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="O155" s="2">
         <v>0</v>
@@ -17050,25 +17054,25 @@
         <v>3</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T155" s="2" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="U155" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="W155" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X155" s="3">
         <v>4</v>
       </c>
       <c r="Y155" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Z155" s="2">
         <v>794</v>
@@ -17086,7 +17090,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="156" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>2023</v>
       </c>
@@ -17094,19 +17098,19 @@
         <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>35</v>
@@ -17142,16 +17146,16 @@
         <v>0</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T156" s="4">
         <v>45917</v>
       </c>
       <c r="U156" s="2" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="V156" s="2" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="W156" s="4">
         <v>45719</v>
@@ -17163,13 +17167,13 @@
         <v>45696</v>
       </c>
       <c r="Z156" s="2" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="AA156" s="2">
         <v>45</v>
       </c>
       <c r="AB156" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AC156" s="2">
         <v>623</v>
@@ -17178,7 +17182,7 @@
         <v>45835</v>
       </c>
     </row>
-    <row r="157" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>2023</v>
       </c>
@@ -17186,19 +17190,19 @@
         <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>828</v>
+        <v>772</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>35</v>
@@ -17228,22 +17232,22 @@
         <v>0</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R157" s="2">
         <v>0</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="T157" s="4">
         <v>45753</v>
       </c>
       <c r="U157" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="W157" s="4">
         <v>45690</v>
@@ -17252,10 +17256,10 @@
         <v>1</v>
       </c>
       <c r="Y157" s="2" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="Z157" s="2" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="AA157" s="2">
         <v>15</v>
@@ -17267,11 +17271,12 @@
         <v>337</v>
       </c>
       <c r="AD157" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E157" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AD157" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>